--- a/tables/s3/all/Table_S_linear_comparison_12way_pvalues.xlsx
+++ b/tables/s3/all/Table_S_linear_comparison_12way_pvalues.xlsx
@@ -429,25 +429,25 @@
         <v>2</v>
       </c>
       <c r="E2">
-        <v>0.3532765684145205</v>
+        <v>0.3532765684145226</v>
       </c>
       <c r="F2">
         <v>0.9592068690375832</v>
       </c>
       <c r="G2">
-        <v>0.9592068690375833</v>
+        <v>0.9592068690375831</v>
       </c>
       <c r="H2">
-        <v>0.0002749738173749561</v>
+        <v>0.0002749738173749587</v>
       </c>
       <c r="I2">
         <v>-0.09969752880088767</v>
       </c>
       <c r="J2">
-        <v>24.23489800625105</v>
+        <v>24.23489800625118</v>
       </c>
       <c r="K2">
-        <v>25.68961795561505</v>
+        <v>25.68961795561518</v>
       </c>
     </row>
     <row r="3">
@@ -468,25 +468,25 @@
         <v>2</v>
       </c>
       <c r="E3">
-        <v>0.4007657804695542</v>
+        <v>0.4007659585423482</v>
       </c>
       <c r="F3">
-        <v>0.9299057096157366</v>
+        <v>0.9299060144762135</v>
       </c>
       <c r="G3">
-        <v>0.9299057096157367</v>
+        <v>0.9299060144762137</v>
       </c>
       <c r="H3">
-        <v>0.0008130280377110014</v>
+        <v>0.0008130209501747388</v>
       </c>
       <c r="I3">
-        <v>-0.09910566915851793</v>
+        <v>-0.09910567695480776</v>
       </c>
       <c r="J3">
-        <v>34.64171416888209</v>
+        <v>34.64171657801668</v>
       </c>
       <c r="K3">
-        <v>36.09643411824609</v>
+        <v>36.09643652738068</v>
       </c>
     </row>
     <row r="4">
@@ -507,25 +507,25 @@
         <v>2</v>
       </c>
       <c r="E4">
-        <v>0.2596178295862587</v>
+        <v>0.2596178295862601</v>
       </c>
       <c r="F4">
-        <v>0.5550017655306313</v>
+        <v>0.5550017655306341</v>
       </c>
       <c r="G4">
-        <v>0.5550017655306311</v>
+        <v>0.5550017655306341</v>
       </c>
       <c r="H4">
-        <v>0.03595841375621631</v>
+        <v>0.03595841375621578</v>
       </c>
       <c r="I4">
-        <v>-0.06044574486816212</v>
+        <v>-0.06044574486816279</v>
       </c>
       <c r="J4">
-        <v>37.94561471031825</v>
+        <v>37.9456147103182</v>
       </c>
       <c r="K4">
-        <v>39.40033465968224</v>
+        <v>39.4003346596822</v>
       </c>
     </row>
     <row r="5">
@@ -546,25 +546,25 @@
         <v>3</v>
       </c>
       <c r="E5">
-        <v>0.6876541591966161</v>
+        <v>0.6876541591966195</v>
       </c>
       <c r="F5">
-        <v>0.7781042972612857</v>
+        <v>0.7781042972612839</v>
       </c>
       <c r="G5">
-        <v>0.7781042972612858</v>
+        <v>0.7781042972612838</v>
       </c>
       <c r="H5">
-        <v>0.009282074211127121</v>
+        <v>0.009282074211127289</v>
       </c>
       <c r="I5">
-        <v>-0.1007976953209699</v>
+        <v>-0.1007976953209697</v>
       </c>
       <c r="J5">
-        <v>23.49301957504808</v>
+        <v>23.49301957504819</v>
       </c>
       <c r="K5">
-        <v>24.68670539344319</v>
+        <v>24.6867053934433</v>
       </c>
     </row>
     <row r="6">
@@ -585,25 +585,25 @@
         <v>3</v>
       </c>
       <c r="E6">
-        <v>0.2635902626387136</v>
+        <v>0.2635904174112546</v>
       </c>
       <c r="F6">
-        <v>0.5589032346497287</v>
+        <v>0.5589035160742397</v>
       </c>
       <c r="G6">
-        <v>0.5589032346497286</v>
+        <v>0.5589035160742399</v>
       </c>
       <c r="H6">
-        <v>0.03931846932253291</v>
+        <v>0.03931841416054248</v>
       </c>
       <c r="I6">
-        <v>-0.06742392297496358</v>
+        <v>-0.067423984266064</v>
       </c>
       <c r="J6">
-        <v>32.41460081033853</v>
+        <v>32.41460344564545</v>
       </c>
       <c r="K6">
-        <v>33.60828662873364</v>
+        <v>33.60828926404056</v>
       </c>
     </row>
     <row r="7">
@@ -624,25 +624,25 @@
         <v>3</v>
       </c>
       <c r="E7">
-        <v>0.1219928636081741</v>
+        <v>0.1219928636081726</v>
       </c>
       <c r="F7">
-        <v>0.2413094811759992</v>
+        <v>0.2413094811759975</v>
       </c>
       <c r="G7">
-        <v>0.2413094811759992</v>
+        <v>0.2413094811759975</v>
       </c>
       <c r="H7">
-        <v>0.1488083216059171</v>
+        <v>0.1488083216059181</v>
       </c>
       <c r="I7">
-        <v>0.05423146845101889</v>
+        <v>0.05423146845102</v>
       </c>
       <c r="J7">
-        <v>34.62260230515962</v>
+        <v>34.62260230515953</v>
       </c>
       <c r="K7">
-        <v>35.81628812355473</v>
+        <v>35.81628812355465</v>
       </c>
     </row>
     <row r="8">
@@ -663,25 +663,25 @@
         <v>3</v>
       </c>
       <c r="E8">
-        <v>0.3497037335674026</v>
+        <v>0.3497037335674049</v>
       </c>
       <c r="F8">
-        <v>0.9640997800475369</v>
+        <v>0.9640997800475366</v>
       </c>
       <c r="G8">
-        <v>0.964099780047537</v>
+        <v>0.9640997800475368</v>
       </c>
       <c r="H8">
-        <v>0.0002378982173758175</v>
+        <v>0.0002378982173758202</v>
       </c>
       <c r="I8">
         <v>-0.1108467797584713</v>
       </c>
       <c r="J8">
-        <v>23.22887634248282</v>
+        <v>23.22887634248294</v>
       </c>
       <c r="K8">
-        <v>24.42256216087793</v>
+        <v>24.42256216087805</v>
       </c>
     </row>
     <row r="9">
@@ -702,25 +702,25 @@
         <v>3</v>
       </c>
       <c r="E9">
-        <v>0.4337515307822681</v>
+        <v>0.4337517019058801</v>
       </c>
       <c r="F9">
-        <v>0.9344664223346069</v>
+        <v>0.9344667105418158</v>
       </c>
       <c r="G9">
-        <v>0.9344664223346065</v>
+        <v>0.9344667105418158</v>
       </c>
       <c r="H9">
-        <v>0.0007937576249894485</v>
+        <v>0.000793750630390865</v>
       </c>
       <c r="I9">
-        <v>-0.1102291581944561</v>
+        <v>-0.1102291659662324</v>
       </c>
       <c r="J9">
-        <v>33.18336258693958</v>
+        <v>33.18336485446272</v>
       </c>
       <c r="K9">
-        <v>34.37704840533469</v>
+        <v>34.37705067285783</v>
       </c>
     </row>
     <row r="10">
@@ -741,25 +741,25 @@
         <v>3</v>
       </c>
       <c r="E10">
-        <v>0.2946144756849663</v>
+        <v>0.2946144756849679</v>
       </c>
       <c r="F10">
-        <v>0.5760922793434635</v>
+        <v>0.5760922793434665</v>
       </c>
       <c r="G10">
-        <v>0.5760922793434635</v>
+        <v>0.5760922793434664</v>
       </c>
       <c r="H10">
-        <v>0.03604075856133827</v>
+        <v>0.03604075856133777</v>
       </c>
       <c r="I10">
-        <v>-0.07106582382073534</v>
+        <v>-0.07106582382073579</v>
       </c>
       <c r="J10">
-        <v>36.12952731002768</v>
+        <v>36.12952731002763</v>
       </c>
       <c r="K10">
-        <v>37.32321312842279</v>
+        <v>37.32321312842274</v>
       </c>
     </row>
     <row r="11">
@@ -780,25 +780,25 @@
         <v>4</v>
       </c>
       <c r="E11">
-        <v>0.6503872683131052</v>
+        <v>0.6503872683131071</v>
       </c>
       <c r="F11">
-        <v>0.8240060454694407</v>
+        <v>0.8240060454694405</v>
       </c>
       <c r="G11">
-        <v>0.8240060454694407</v>
+        <v>0.8240060454694402</v>
       </c>
       <c r="H11">
-        <v>0.006558312211902245</v>
+        <v>0.006558312211902282</v>
       </c>
       <c r="I11">
         <v>-0.11762189876161</v>
       </c>
       <c r="J11">
-        <v>22.50508856659826</v>
+        <v>22.50508856659837</v>
       </c>
       <c r="K11">
-        <v>23.4128438455804</v>
+        <v>23.41284384558051</v>
       </c>
     </row>
     <row r="12">
@@ -819,25 +819,25 @@
         <v>4</v>
       </c>
       <c r="E12">
-        <v>0.3010840984136101</v>
+        <v>0.3010842492531833</v>
       </c>
       <c r="F12">
-        <v>0.5872956603060915</v>
+        <v>0.5872959229113653</v>
       </c>
       <c r="G12">
-        <v>0.5872956603060911</v>
+        <v>0.5872959229113652</v>
       </c>
       <c r="H12">
-        <v>0.03842588172195213</v>
+        <v>0.038425828786233</v>
       </c>
       <c r="I12">
-        <v>-0.08177088306280389</v>
+        <v>-0.08177094261548778</v>
       </c>
       <c r="J12">
-        <v>30.96304634863998</v>
+        <v>30.96304876125316</v>
       </c>
       <c r="K12">
-        <v>31.87080162762212</v>
+        <v>31.8708040402353</v>
       </c>
     </row>
     <row r="13">
@@ -858,25 +858,25 @@
         <v>4</v>
       </c>
       <c r="E13">
-        <v>0.1545553549140538</v>
+        <v>0.154555354914052</v>
       </c>
       <c r="F13">
-        <v>0.2774828293025933</v>
+        <v>0.2774828293025911</v>
       </c>
       <c r="G13">
-        <v>0.277482829302593</v>
+        <v>0.2774828293025909</v>
       </c>
       <c r="H13">
-        <v>0.1450992847480247</v>
+        <v>0.145099284748026</v>
       </c>
       <c r="I13">
-        <v>0.03823669534152785</v>
+        <v>0.03823669534152918</v>
       </c>
       <c r="J13">
-        <v>32.94015383098684</v>
+        <v>32.94015383098678</v>
       </c>
       <c r="K13">
-        <v>33.84790910996898</v>
+        <v>33.84790910996892</v>
       </c>
     </row>
   </sheetData>

--- a/tables/s3/all/Table_S_linear_comparison_12way_pvalues.xlsx
+++ b/tables/s3/all/Table_S_linear_comparison_12way_pvalues.xlsx
@@ -429,25 +429,25 @@
         <v>2</v>
       </c>
       <c r="E2">
-        <v>0.3532765684145226</v>
+        <v>0.4253188742317375</v>
       </c>
       <c r="F2">
-        <v>0.9592068690375832</v>
+        <v>0.9335953671517381</v>
       </c>
       <c r="G2">
-        <v>0.9592068690375831</v>
+        <v>0.9335953671517381</v>
       </c>
       <c r="H2">
-        <v>0.0002749738173749587</v>
+        <v>0.0007295252435131165</v>
       </c>
       <c r="I2">
-        <v>-0.09969752880088767</v>
+        <v>-0.09919752223213574</v>
       </c>
       <c r="J2">
-        <v>24.23489800625118</v>
+        <v>33.30904866970052</v>
       </c>
       <c r="K2">
-        <v>25.68961795561518</v>
+        <v>34.76376861906452</v>
       </c>
     </row>
     <row r="3">
@@ -468,25 +468,25 @@
         <v>2</v>
       </c>
       <c r="E3">
-        <v>0.4007659585423482</v>
+        <v>0.6315475910089493</v>
       </c>
       <c r="F3">
-        <v>0.9299060144762135</v>
+        <v>0.4747445482107494</v>
       </c>
       <c r="G3">
-        <v>0.9299060144762137</v>
+        <v>0.4747445482107496</v>
       </c>
       <c r="H3">
-        <v>0.0008130209501747388</v>
+        <v>0.05227761316830168</v>
       </c>
       <c r="I3">
-        <v>-0.09910567695480776</v>
+        <v>-0.04249462551486816</v>
       </c>
       <c r="J3">
-        <v>34.64171657801668</v>
+        <v>518.2280877889636</v>
       </c>
       <c r="K3">
-        <v>36.09643652738068</v>
+        <v>519.6828077383276</v>
       </c>
     </row>
     <row r="4">
@@ -507,25 +507,25 @@
         <v>2</v>
       </c>
       <c r="E4">
-        <v>0.2596178295862601</v>
+        <v>0.2650086305626576</v>
       </c>
       <c r="F4">
-        <v>0.5550017655306341</v>
+        <v>0.7007065603216986</v>
       </c>
       <c r="G4">
-        <v>0.5550017655306341</v>
+        <v>0.7007065603216985</v>
       </c>
       <c r="H4">
-        <v>0.03595841375621578</v>
+        <v>0.015408974213204</v>
       </c>
       <c r="I4">
-        <v>-0.06044574486816279</v>
+        <v>-0.08305012836547565</v>
       </c>
       <c r="J4">
-        <v>37.9456147103182</v>
+        <v>28.9597736282219</v>
       </c>
       <c r="K4">
-        <v>39.4003346596822</v>
+        <v>30.4144935775859</v>
       </c>
     </row>
     <row r="5">
@@ -546,25 +546,25 @@
         <v>3</v>
       </c>
       <c r="E5">
-        <v>0.6876541591966195</v>
+        <v>0.9142943127840686</v>
       </c>
       <c r="F5">
-        <v>0.7781042972612839</v>
+        <v>0.6139193894159656</v>
       </c>
       <c r="G5">
-        <v>0.7781042972612838</v>
+        <v>0.6139193894159662</v>
       </c>
       <c r="H5">
-        <v>0.009282074211127289</v>
+        <v>0.02944413603604164</v>
       </c>
       <c r="I5">
-        <v>-0.1007976953209697</v>
+        <v>-0.07839540440439818</v>
       </c>
       <c r="J5">
-        <v>23.49301957504819</v>
+        <v>31.40668128630793</v>
       </c>
       <c r="K5">
-        <v>24.6867053934433</v>
+        <v>32.60036710470304</v>
       </c>
     </row>
     <row r="6">
@@ -585,25 +585,25 @@
         <v>3</v>
       </c>
       <c r="E6">
-        <v>0.2635904174112546</v>
+        <v>0.6228669674107681</v>
       </c>
       <c r="F6">
-        <v>0.5589035160742397</v>
+        <v>0.5061122098143548</v>
       </c>
       <c r="G6">
-        <v>0.5589035160742399</v>
+        <v>0.5061122098143548</v>
       </c>
       <c r="H6">
-        <v>0.03931841416054248</v>
+        <v>0.05058485356562643</v>
       </c>
       <c r="I6">
-        <v>-0.067423984266064</v>
+        <v>-0.05490571826041513</v>
       </c>
       <c r="J6">
-        <v>32.41460344564545</v>
+        <v>476.427882076899</v>
       </c>
       <c r="K6">
-        <v>33.60828926404056</v>
+        <v>477.6215678952941</v>
       </c>
     </row>
     <row r="7">
@@ -624,25 +624,25 @@
         <v>3</v>
       </c>
       <c r="E7">
-        <v>0.1219928636081726</v>
+        <v>0.7011133204167393</v>
       </c>
       <c r="F7">
-        <v>0.2413094811759975</v>
+        <v>0.4956376505110552</v>
       </c>
       <c r="G7">
-        <v>0.2413094811759975</v>
+        <v>0.4956376505110555</v>
       </c>
       <c r="H7">
-        <v>0.1488083216059181</v>
+        <v>0.05305217852030607</v>
       </c>
       <c r="I7">
-        <v>0.05423146845102</v>
+        <v>-0.05216424608854875</v>
       </c>
       <c r="J7">
-        <v>34.62260230515953</v>
+        <v>27.51296442658087</v>
       </c>
       <c r="K7">
-        <v>35.81628812355465</v>
+        <v>28.70665024497598</v>
       </c>
     </row>
     <row r="8">
@@ -663,25 +663,25 @@
         <v>3</v>
       </c>
       <c r="E8">
-        <v>0.3497037335674049</v>
+        <v>0.414844841581346</v>
       </c>
       <c r="F8">
-        <v>0.9640997800475366</v>
+        <v>0.9394273734706236</v>
       </c>
       <c r="G8">
-        <v>0.9640997800475368</v>
+        <v>0.9394273734706238</v>
       </c>
       <c r="H8">
-        <v>0.0002378982173758202</v>
+        <v>0.0006779468347169535</v>
       </c>
       <c r="I8">
-        <v>-0.1108467797584713</v>
+        <v>-0.1103578368503144</v>
       </c>
       <c r="J8">
-        <v>23.22887634248294</v>
+        <v>31.48167110199321</v>
       </c>
       <c r="K8">
-        <v>24.42256216087805</v>
+        <v>32.67535692038832</v>
       </c>
     </row>
     <row r="9">
@@ -702,25 +702,25 @@
         <v>3</v>
       </c>
       <c r="E9">
-        <v>0.4337517019058801</v>
+        <v>0.6643580348850944</v>
       </c>
       <c r="F9">
-        <v>0.9344667105418158</v>
+        <v>0.4983418507122158</v>
       </c>
       <c r="G9">
-        <v>0.9344667105418158</v>
+        <v>0.4983418507122159</v>
       </c>
       <c r="H9">
-        <v>0.000793750630390865</v>
+        <v>0.0524073955136062</v>
       </c>
       <c r="I9">
-        <v>-0.1102291659662324</v>
+        <v>-0.05288067165154864</v>
       </c>
       <c r="J9">
-        <v>33.18336485446272</v>
+        <v>476.4067456639754</v>
       </c>
       <c r="K9">
-        <v>34.37705067285783</v>
+        <v>477.6004314823705</v>
       </c>
     </row>
     <row r="10">
@@ -741,25 +741,25 @@
         <v>3</v>
       </c>
       <c r="E10">
-        <v>0.2946144756849679</v>
+        <v>0.2408979019988763</v>
       </c>
       <c r="F10">
-        <v>0.5760922793434665</v>
+        <v>0.706735810244882</v>
       </c>
       <c r="G10">
-        <v>0.5760922793434664</v>
+        <v>0.706735810244882</v>
       </c>
       <c r="H10">
-        <v>0.03604075856133777</v>
+        <v>0.01648671948118549</v>
       </c>
       <c r="I10">
-        <v>-0.07106582382073579</v>
+        <v>-0.09279253390979392</v>
       </c>
       <c r="J10">
-        <v>36.12952731002763</v>
+        <v>26.83089432290748</v>
       </c>
       <c r="K10">
-        <v>37.32321312842274</v>
+        <v>28.02458014130259</v>
       </c>
     </row>
     <row r="11">
@@ -780,25 +780,25 @@
         <v>4</v>
       </c>
       <c r="E11">
-        <v>0.6503872683131071</v>
+        <v>0.8589524661905621</v>
       </c>
       <c r="F11">
-        <v>0.8240060454694405</v>
+        <v>0.6640368850813131</v>
       </c>
       <c r="G11">
-        <v>0.8240060454694402</v>
+        <v>0.6640368850813131</v>
       </c>
       <c r="H11">
-        <v>0.006558312211902282</v>
+        <v>0.02478326676865925</v>
       </c>
       <c r="I11">
-        <v>-0.11762189876161</v>
+        <v>-0.09711882488525836</v>
       </c>
       <c r="J11">
-        <v>22.50508856659837</v>
+        <v>29.68154686827921</v>
       </c>
       <c r="K11">
-        <v>23.41284384558051</v>
+        <v>30.58930214726134</v>
       </c>
     </row>
     <row r="12">
@@ -819,25 +819,25 @@
         <v>4</v>
       </c>
       <c r="E12">
-        <v>0.3010842492531833</v>
+        <v>0.6692516072333043</v>
       </c>
       <c r="F12">
-        <v>0.5872959229113653</v>
+        <v>0.5452557154988897</v>
       </c>
       <c r="G12">
-        <v>0.5872959229113652</v>
+        <v>0.5452557154988897</v>
       </c>
       <c r="H12">
-        <v>0.038425828786233</v>
+        <v>0.04749941142062517</v>
       </c>
       <c r="I12">
-        <v>-0.08177094261548778</v>
+        <v>-0.0715631621517967</v>
       </c>
       <c r="J12">
-        <v>30.96304876125316</v>
+        <v>434.5467550701834</v>
       </c>
       <c r="K12">
-        <v>31.8708040402353</v>
+        <v>435.4545103491656</v>
       </c>
     </row>
     <row r="13">
@@ -858,25 +858,25 @@
         <v>4</v>
       </c>
       <c r="E13">
-        <v>0.154555354914052</v>
+        <v>0.6204297844730287</v>
       </c>
       <c r="F13">
-        <v>0.2774828293025911</v>
+        <v>0.5527664765546055</v>
       </c>
       <c r="G13">
-        <v>0.2774828293025909</v>
+        <v>0.5527664765546054</v>
       </c>
       <c r="H13">
-        <v>0.145099284748026</v>
+        <v>0.04578792186942378</v>
       </c>
       <c r="I13">
-        <v>0.03823669534152918</v>
+        <v>-0.07348858789689827</v>
       </c>
       <c r="J13">
-        <v>32.94015383098678</v>
+        <v>25.56399455982545</v>
       </c>
       <c r="K13">
-        <v>33.84790910996892</v>
+        <v>26.47174983880759</v>
       </c>
     </row>
   </sheetData>

--- a/tables/s3/all/Table_S_linear_comparison_12way_pvalues.xlsx
+++ b/tables/s3/all/Table_S_linear_comparison_12way_pvalues.xlsx
@@ -429,25 +429,25 @@
         <v>2</v>
       </c>
       <c r="E2">
-        <v>0.4253188742317375</v>
+        <v>0.3508016532603971</v>
       </c>
       <c r="F2">
-        <v>0.9335953671517381</v>
+        <v>0.9857245248628008</v>
       </c>
       <c r="G2">
-        <v>0.9335953671517381</v>
+        <v>0.985724524862801</v>
       </c>
       <c r="H2">
-        <v>0.0007295252435131165</v>
+        <v>3.365262523438211E-05</v>
       </c>
       <c r="I2">
-        <v>-0.09919752223213574</v>
+        <v>-0.0999629821122423</v>
       </c>
       <c r="J2">
-        <v>33.30904866970052</v>
+        <v>29.36716491208817</v>
       </c>
       <c r="K2">
-        <v>34.76376861906452</v>
+        <v>30.82188486145217</v>
       </c>
     </row>
     <row r="3">
@@ -468,25 +468,25 @@
         <v>2</v>
       </c>
       <c r="E3">
-        <v>0.6315475910089493</v>
+        <v>0.03532929419869479</v>
       </c>
       <c r="F3">
-        <v>0.4747445482107494</v>
+        <v>0.05598621230796001</v>
       </c>
       <c r="G3">
-        <v>0.4747445482107496</v>
+        <v>0.05598621230796001</v>
       </c>
       <c r="H3">
-        <v>0.05227761316830168</v>
+        <v>0.3183939864367406</v>
       </c>
       <c r="I3">
-        <v>-0.04249462551486816</v>
+        <v>0.2502333850804147</v>
       </c>
       <c r="J3">
-        <v>518.2280877889636</v>
+        <v>22.13444877953392</v>
       </c>
       <c r="K3">
-        <v>519.6828077383276</v>
+        <v>23.58916872889792</v>
       </c>
     </row>
     <row r="4">
@@ -507,25 +507,25 @@
         <v>2</v>
       </c>
       <c r="E4">
-        <v>0.2650086305626576</v>
+        <v>0.02632775285351801</v>
       </c>
       <c r="F4">
-        <v>0.7007065603216986</v>
+        <v>0.04864751758991975</v>
       </c>
       <c r="G4">
-        <v>0.7007065603216985</v>
+        <v>0.0486475175899197</v>
       </c>
       <c r="H4">
-        <v>0.015408974213204</v>
+        <v>0.3349697104001809</v>
       </c>
       <c r="I4">
-        <v>-0.08305012836547565</v>
+        <v>0.2684666814401989</v>
       </c>
       <c r="J4">
-        <v>28.9597736282219</v>
+        <v>20.87103123969536</v>
       </c>
       <c r="K4">
-        <v>30.4144935775859</v>
+        <v>22.32575118905936</v>
       </c>
     </row>
     <row r="5">
@@ -546,25 +546,25 @@
         <v>3</v>
       </c>
       <c r="E5">
-        <v>0.9142943127840686</v>
+        <v>0.8384614020309604</v>
       </c>
       <c r="F5">
-        <v>0.6139193894159656</v>
+        <v>0.6432908516280571</v>
       </c>
       <c r="G5">
-        <v>0.6139193894159662</v>
+        <v>0.6432908516280571</v>
       </c>
       <c r="H5">
-        <v>0.02944413603604164</v>
+        <v>0.02487023481662192</v>
       </c>
       <c r="I5">
-        <v>-0.07839540440439818</v>
+        <v>-0.08347751687042027</v>
       </c>
       <c r="J5">
-        <v>31.40668128630793</v>
+        <v>27.77866608192901</v>
       </c>
       <c r="K5">
-        <v>32.60036710470304</v>
+        <v>28.97235190032413</v>
       </c>
     </row>
     <row r="6">
@@ -585,25 +585,25 @@
         <v>3</v>
       </c>
       <c r="E6">
-        <v>0.6228669674107681</v>
+        <v>0.1352231876127085</v>
       </c>
       <c r="F6">
-        <v>0.5061122098143548</v>
+        <v>0.1659053936123868</v>
       </c>
       <c r="G6">
-        <v>0.5061122098143548</v>
+        <v>0.1659053936123868</v>
       </c>
       <c r="H6">
-        <v>0.05058485356562643</v>
+        <v>0.2016410903691337</v>
       </c>
       <c r="I6">
-        <v>-0.05490571826041513</v>
+        <v>0.112934544854593</v>
       </c>
       <c r="J6">
-        <v>476.427882076899</v>
+        <v>21.74263053983506</v>
       </c>
       <c r="K6">
-        <v>477.6215678952941</v>
+        <v>22.93631635823017</v>
       </c>
     </row>
     <row r="7">
@@ -624,25 +624,25 @@
         <v>3</v>
       </c>
       <c r="E7">
-        <v>0.7011133204167393</v>
+        <v>0.154740676256274</v>
       </c>
       <c r="F7">
-        <v>0.4956376505110552</v>
+        <v>0.2043690961520518</v>
       </c>
       <c r="G7">
-        <v>0.4956376505110555</v>
+        <v>0.2043690961520518</v>
       </c>
       <c r="H7">
-        <v>0.05305217852030607</v>
+        <v>0.1722268361960219</v>
       </c>
       <c r="I7">
-        <v>-0.05216424608854875</v>
+        <v>0.08025204021780219</v>
       </c>
       <c r="J7">
-        <v>27.51296442658087</v>
+        <v>20.41197796065431</v>
       </c>
       <c r="K7">
-        <v>28.70665024497598</v>
+        <v>21.60566377904942</v>
       </c>
     </row>
     <row r="8">
@@ -663,25 +663,25 @@
         <v>3</v>
       </c>
       <c r="E8">
-        <v>0.414844841581346</v>
+        <v>0.3414467889800145</v>
       </c>
       <c r="F8">
-        <v>0.9394273734706236</v>
+        <v>0.9901323226621296</v>
       </c>
       <c r="G8">
-        <v>0.9394273734706238</v>
+        <v>0.9901323226621297</v>
       </c>
       <c r="H8">
-        <v>0.0006779468347169535</v>
+        <v>1.796403892937554E-05</v>
       </c>
       <c r="I8">
-        <v>-0.1103578368503144</v>
+        <v>-0.1110911510678563</v>
       </c>
       <c r="J8">
-        <v>31.48167110199321</v>
+        <v>27.79592340336841</v>
       </c>
       <c r="K8">
-        <v>32.67535692038832</v>
+        <v>28.98960922176352</v>
       </c>
     </row>
     <row r="9">
@@ -702,25 +702,25 @@
         <v>3</v>
       </c>
       <c r="E9">
-        <v>0.6643580348850944</v>
+        <v>0.04752918207841706</v>
       </c>
       <c r="F9">
-        <v>0.4983418507122158</v>
+        <v>0.07049951671919756</v>
       </c>
       <c r="G9">
-        <v>0.4983418507122159</v>
+        <v>0.07049951671919756</v>
       </c>
       <c r="H9">
-        <v>0.0524073955136062</v>
+        <v>0.3185227609170402</v>
       </c>
       <c r="I9">
-        <v>-0.05288067165154864</v>
+        <v>0.2428030676856002</v>
       </c>
       <c r="J9">
-        <v>476.4067456639754</v>
+        <v>21.73078840867091</v>
       </c>
       <c r="K9">
-        <v>477.6004314823705</v>
+        <v>22.92447422706602</v>
       </c>
     </row>
     <row r="10">
@@ -741,25 +741,25 @@
         <v>3</v>
       </c>
       <c r="E10">
-        <v>0.2408979019988763</v>
+        <v>0.03613637571524328</v>
       </c>
       <c r="F10">
-        <v>0.706735810244882</v>
+        <v>0.06212614755094788</v>
       </c>
       <c r="G10">
-        <v>0.706735810244882</v>
+        <v>0.06212614755094788</v>
       </c>
       <c r="H10">
-        <v>0.01648671948118549</v>
+        <v>0.3349335328048116</v>
       </c>
       <c r="I10">
-        <v>-0.09279253390979392</v>
+        <v>0.2610372586720128</v>
       </c>
       <c r="J10">
-        <v>26.83089432290748</v>
+        <v>20.58769695808868</v>
       </c>
       <c r="K10">
-        <v>28.02458014130259</v>
+        <v>21.7813827764838</v>
       </c>
     </row>
     <row r="11">
@@ -780,25 +780,25 @@
         <v>4</v>
       </c>
       <c r="E11">
-        <v>0.8589524661905621</v>
+        <v>0.7831773928287253</v>
       </c>
       <c r="F11">
-        <v>0.6640368850813131</v>
+        <v>0.6947961370722957</v>
       </c>
       <c r="G11">
-        <v>0.6640368850813131</v>
+        <v>0.6947961370722957</v>
       </c>
       <c r="H11">
-        <v>0.02478326676865925</v>
+        <v>0.02026999469599338</v>
       </c>
       <c r="I11">
-        <v>-0.09711882488525836</v>
+        <v>-0.1021962559670075</v>
       </c>
       <c r="J11">
-        <v>29.68154686827921</v>
+        <v>26.32366657378503</v>
       </c>
       <c r="K11">
-        <v>30.58930214726134</v>
+        <v>27.23142185276717</v>
       </c>
     </row>
     <row r="12">
@@ -819,25 +819,25 @@
         <v>4</v>
       </c>
       <c r="E12">
-        <v>0.6692516072333043</v>
+        <v>0.1680299861036016</v>
       </c>
       <c r="F12">
-        <v>0.5452557154988897</v>
+        <v>0.1971935301958709</v>
       </c>
       <c r="G12">
-        <v>0.5452557154988897</v>
+        <v>0.1971935301958712</v>
       </c>
       <c r="H12">
-        <v>0.04749941142062517</v>
+        <v>0.1982700497975259</v>
       </c>
       <c r="I12">
-        <v>-0.0715631621517967</v>
+        <v>0.09805380602221658</v>
       </c>
       <c r="J12">
-        <v>434.5467550701834</v>
+        <v>21.24751166928304</v>
       </c>
       <c r="K12">
-        <v>435.4545103491656</v>
+        <v>22.15526694826518</v>
       </c>
     </row>
     <row r="13">
@@ -858,25 +858,25 @@
         <v>4</v>
       </c>
       <c r="E13">
-        <v>0.6204297844730287</v>
+        <v>0.1880526673652805</v>
       </c>
       <c r="F13">
-        <v>0.5527664765546055</v>
+        <v>0.2368596318115311</v>
       </c>
       <c r="G13">
-        <v>0.5527664765546054</v>
+        <v>0.2368596318115311</v>
       </c>
       <c r="H13">
-        <v>0.04578792186942378</v>
+        <v>0.1696921444590826</v>
       </c>
       <c r="I13">
-        <v>-0.07348858789689827</v>
+        <v>0.06590366251646795</v>
       </c>
       <c r="J13">
-        <v>25.56399455982545</v>
+        <v>20.04764027978902</v>
       </c>
       <c r="K13">
-        <v>26.47174983880759</v>
+        <v>20.95539555877116</v>
       </c>
     </row>
   </sheetData>

--- a/tables/s3/all/Table_S_linear_comparison_12way_pvalues.xlsx
+++ b/tables/s3/all/Table_S_linear_comparison_12way_pvalues.xlsx
@@ -426,28 +426,28 @@
         <v>12</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>0.3508016532603971</v>
+        <v>0.3532765684145226</v>
       </c>
       <c r="F2">
-        <v>0.9857245248628008</v>
+        <v>0.9592068690375832</v>
       </c>
       <c r="G2">
-        <v>0.985724524862801</v>
+        <v>0.9592068690375831</v>
       </c>
       <c r="H2">
-        <v>3.365262523438211E-05</v>
+        <v>0.0002749738173749587</v>
       </c>
       <c r="I2">
-        <v>-0.0999629821122423</v>
+        <v>-0.09969752880088767</v>
       </c>
       <c r="J2">
-        <v>29.36716491208817</v>
+        <v>24.23489800625118</v>
       </c>
       <c r="K2">
-        <v>30.82188486145217</v>
+        <v>25.68961795561518</v>
       </c>
     </row>
     <row r="3">
@@ -465,28 +465,28 @@
         <v>12</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>0.03532929419869479</v>
+        <v>0.4007659585423482</v>
       </c>
       <c r="F3">
-        <v>0.05598621230796001</v>
+        <v>0.9299060144762135</v>
       </c>
       <c r="G3">
-        <v>0.05598621230796001</v>
+        <v>0.9299060144762137</v>
       </c>
       <c r="H3">
-        <v>0.3183939864367406</v>
+        <v>0.0008130209501747388</v>
       </c>
       <c r="I3">
-        <v>0.2502333850804147</v>
+        <v>-0.09910567695480776</v>
       </c>
       <c r="J3">
-        <v>22.13444877953392</v>
+        <v>34.64171657801668</v>
       </c>
       <c r="K3">
-        <v>23.58916872889792</v>
+        <v>36.09643652738068</v>
       </c>
     </row>
     <row r="4">
@@ -504,28 +504,28 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>0.02632775285351801</v>
+        <v>0.2596178295862601</v>
       </c>
       <c r="F4">
-        <v>0.04864751758991975</v>
+        <v>0.5550017655306341</v>
       </c>
       <c r="G4">
-        <v>0.0486475175899197</v>
+        <v>0.5550017655306341</v>
       </c>
       <c r="H4">
-        <v>0.3349697104001809</v>
+        <v>0.03595841375621578</v>
       </c>
       <c r="I4">
-        <v>0.2684666814401989</v>
+        <v>-0.06044574486816279</v>
       </c>
       <c r="J4">
-        <v>20.87103123969536</v>
+        <v>37.9456147103182</v>
       </c>
       <c r="K4">
-        <v>22.32575118905936</v>
+        <v>39.4003346596822</v>
       </c>
     </row>
     <row r="5">
@@ -543,28 +543,28 @@
         <v>11</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>0.8384614020309604</v>
+        <v>0.6876541591966195</v>
       </c>
       <c r="F5">
-        <v>0.6432908516280571</v>
+        <v>0.7781042972612839</v>
       </c>
       <c r="G5">
-        <v>0.6432908516280571</v>
+        <v>0.7781042972612838</v>
       </c>
       <c r="H5">
-        <v>0.02487023481662192</v>
+        <v>0.009282074211127289</v>
       </c>
       <c r="I5">
-        <v>-0.08347751687042027</v>
+        <v>-0.1007976953209697</v>
       </c>
       <c r="J5">
-        <v>27.77866608192901</v>
+        <v>23.49301957504819</v>
       </c>
       <c r="K5">
-        <v>28.97235190032413</v>
+        <v>24.6867053934433</v>
       </c>
     </row>
     <row r="6">
@@ -582,28 +582,28 @@
         <v>11</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>0.1352231876127085</v>
+        <v>0.2635904174112546</v>
       </c>
       <c r="F6">
-        <v>0.1659053936123868</v>
+        <v>0.5589035160742397</v>
       </c>
       <c r="G6">
-        <v>0.1659053936123868</v>
+        <v>0.5589035160742399</v>
       </c>
       <c r="H6">
-        <v>0.2016410903691337</v>
+        <v>0.03931841416054248</v>
       </c>
       <c r="I6">
-        <v>0.112934544854593</v>
+        <v>-0.067423984266064</v>
       </c>
       <c r="J6">
-        <v>21.74263053983506</v>
+        <v>32.41460344564545</v>
       </c>
       <c r="K6">
-        <v>22.93631635823017</v>
+        <v>33.60828926404056</v>
       </c>
     </row>
     <row r="7">
@@ -621,28 +621,28 @@
         <v>11</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>0.154740676256274</v>
+        <v>0.1219928636081726</v>
       </c>
       <c r="F7">
-        <v>0.2043690961520518</v>
+        <v>0.2413094811759975</v>
       </c>
       <c r="G7">
-        <v>0.2043690961520518</v>
+        <v>0.2413094811759975</v>
       </c>
       <c r="H7">
-        <v>0.1722268361960219</v>
+        <v>0.1488083216059181</v>
       </c>
       <c r="I7">
-        <v>0.08025204021780219</v>
+        <v>0.05423146845102</v>
       </c>
       <c r="J7">
-        <v>20.41197796065431</v>
+        <v>34.62260230515953</v>
       </c>
       <c r="K7">
-        <v>21.60566377904942</v>
+        <v>35.81628812355465</v>
       </c>
     </row>
     <row r="8">
@@ -660,28 +660,28 @@
         <v>11</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>0.3414467889800145</v>
+        <v>0.3497037335674049</v>
       </c>
       <c r="F8">
-        <v>0.9901323226621296</v>
+        <v>0.9640997800475366</v>
       </c>
       <c r="G8">
-        <v>0.9901323226621297</v>
+        <v>0.9640997800475368</v>
       </c>
       <c r="H8">
-        <v>1.796403892937554E-05</v>
+        <v>0.0002378982173758202</v>
       </c>
       <c r="I8">
-        <v>-0.1110911510678563</v>
+        <v>-0.1108467797584713</v>
       </c>
       <c r="J8">
-        <v>27.79592340336841</v>
+        <v>23.22887634248294</v>
       </c>
       <c r="K8">
-        <v>28.98960922176352</v>
+        <v>24.42256216087805</v>
       </c>
     </row>
     <row r="9">
@@ -699,28 +699,28 @@
         <v>11</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>0.04752918207841706</v>
+        <v>0.4337517019058801</v>
       </c>
       <c r="F9">
-        <v>0.07049951671919756</v>
+        <v>0.9344667105418158</v>
       </c>
       <c r="G9">
-        <v>0.07049951671919756</v>
+        <v>0.9344667105418158</v>
       </c>
       <c r="H9">
-        <v>0.3185227609170402</v>
+        <v>0.000793750630390865</v>
       </c>
       <c r="I9">
-        <v>0.2428030676856002</v>
+        <v>-0.1102291659662324</v>
       </c>
       <c r="J9">
-        <v>21.73078840867091</v>
+        <v>33.18336485446272</v>
       </c>
       <c r="K9">
-        <v>22.92447422706602</v>
+        <v>34.37705067285783</v>
       </c>
     </row>
     <row r="10">
@@ -738,28 +738,28 @@
         <v>11</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10">
-        <v>0.03613637571524328</v>
+        <v>0.2946144756849679</v>
       </c>
       <c r="F10">
-        <v>0.06212614755094788</v>
+        <v>0.5760922793434665</v>
       </c>
       <c r="G10">
-        <v>0.06212614755094788</v>
+        <v>0.5760922793434664</v>
       </c>
       <c r="H10">
-        <v>0.3349335328048116</v>
+        <v>0.03604075856133777</v>
       </c>
       <c r="I10">
-        <v>0.2610372586720128</v>
+        <v>-0.07106582382073579</v>
       </c>
       <c r="J10">
-        <v>20.58769695808868</v>
+        <v>36.12952731002763</v>
       </c>
       <c r="K10">
-        <v>21.7813827764838</v>
+        <v>37.32321312842274</v>
       </c>
     </row>
     <row r="11">
@@ -777,28 +777,28 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11">
-        <v>0.7831773928287253</v>
+        <v>0.6503872683131071</v>
       </c>
       <c r="F11">
-        <v>0.6947961370722957</v>
+        <v>0.8240060454694405</v>
       </c>
       <c r="G11">
-        <v>0.6947961370722957</v>
+        <v>0.8240060454694402</v>
       </c>
       <c r="H11">
-        <v>0.02026999469599338</v>
+        <v>0.006558312211902282</v>
       </c>
       <c r="I11">
-        <v>-0.1021962559670075</v>
+        <v>-0.11762189876161</v>
       </c>
       <c r="J11">
-        <v>26.32366657378503</v>
+        <v>22.50508856659837</v>
       </c>
       <c r="K11">
-        <v>27.23142185276717</v>
+        <v>23.41284384558051</v>
       </c>
     </row>
     <row r="12">
@@ -816,28 +816,28 @@
         <v>10</v>
       </c>
       <c r="D12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12">
-        <v>0.1680299861036016</v>
+        <v>0.3010842492531833</v>
       </c>
       <c r="F12">
-        <v>0.1971935301958709</v>
+        <v>0.5872959229113653</v>
       </c>
       <c r="G12">
-        <v>0.1971935301958712</v>
+        <v>0.5872959229113652</v>
       </c>
       <c r="H12">
-        <v>0.1982700497975259</v>
+        <v>0.038425828786233</v>
       </c>
       <c r="I12">
-        <v>0.09805380602221658</v>
+        <v>-0.08177094261548778</v>
       </c>
       <c r="J12">
-        <v>21.24751166928304</v>
+        <v>30.96304876125316</v>
       </c>
       <c r="K12">
-        <v>22.15526694826518</v>
+        <v>31.8708040402353</v>
       </c>
     </row>
     <row r="13">
@@ -855,28 +855,28 @@
         <v>10</v>
       </c>
       <c r="D13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E13">
-        <v>0.1880526673652805</v>
+        <v>0.154555354914052</v>
       </c>
       <c r="F13">
-        <v>0.2368596318115311</v>
+        <v>0.2774828293025911</v>
       </c>
       <c r="G13">
-        <v>0.2368596318115311</v>
+        <v>0.2774828293025909</v>
       </c>
       <c r="H13">
-        <v>0.1696921444590826</v>
+        <v>0.145099284748026</v>
       </c>
       <c r="I13">
-        <v>0.06590366251646795</v>
+        <v>0.03823669534152918</v>
       </c>
       <c r="J13">
-        <v>20.04764027978902</v>
+        <v>32.94015383098678</v>
       </c>
       <c r="K13">
-        <v>20.95539555877116</v>
+        <v>33.84790910996892</v>
       </c>
     </row>
   </sheetData>

--- a/tables/s3/all/Table_S_linear_comparison_12way_pvalues.xlsx
+++ b/tables/s3/all/Table_S_linear_comparison_12way_pvalues.xlsx
@@ -426,28 +426,28 @@
         <v>12</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>0.3532765684145226</v>
+        <v>0.3508016532603971</v>
       </c>
       <c r="F2">
-        <v>0.9592068690375832</v>
+        <v>0.9857245248628008</v>
       </c>
       <c r="G2">
-        <v>0.9592068690375831</v>
+        <v>0.985724524862801</v>
       </c>
       <c r="H2">
-        <v>0.0002749738173749587</v>
+        <v>3.365262523438211E-05</v>
       </c>
       <c r="I2">
-        <v>-0.09969752880088767</v>
+        <v>-0.0999629821122423</v>
       </c>
       <c r="J2">
-        <v>24.23489800625118</v>
+        <v>29.36716491208817</v>
       </c>
       <c r="K2">
-        <v>25.68961795561518</v>
+        <v>30.82188486145217</v>
       </c>
     </row>
     <row r="3">
@@ -465,28 +465,28 @@
         <v>12</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>0.4007659585423482</v>
+        <v>0.03532929419869479</v>
       </c>
       <c r="F3">
-        <v>0.9299060144762135</v>
+        <v>0.05598621230796001</v>
       </c>
       <c r="G3">
-        <v>0.9299060144762137</v>
+        <v>0.05598621230796001</v>
       </c>
       <c r="H3">
-        <v>0.0008130209501747388</v>
+        <v>0.3183939864367406</v>
       </c>
       <c r="I3">
-        <v>-0.09910567695480776</v>
+        <v>0.2502333850804147</v>
       </c>
       <c r="J3">
-        <v>34.64171657801668</v>
+        <v>22.13444877953392</v>
       </c>
       <c r="K3">
-        <v>36.09643652738068</v>
+        <v>23.58916872889792</v>
       </c>
     </row>
     <row r="4">
@@ -504,28 +504,28 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>0.2596178295862601</v>
+        <v>0.02632775285351801</v>
       </c>
       <c r="F4">
-        <v>0.5550017655306341</v>
+        <v>0.04864751758991975</v>
       </c>
       <c r="G4">
-        <v>0.5550017655306341</v>
+        <v>0.0486475175899197</v>
       </c>
       <c r="H4">
-        <v>0.03595841375621578</v>
+        <v>0.3349697104001809</v>
       </c>
       <c r="I4">
-        <v>-0.06044574486816279</v>
+        <v>0.2684666814401989</v>
       </c>
       <c r="J4">
-        <v>37.9456147103182</v>
+        <v>20.87103123969536</v>
       </c>
       <c r="K4">
-        <v>39.4003346596822</v>
+        <v>22.32575118905936</v>
       </c>
     </row>
     <row r="5">
@@ -543,28 +543,28 @@
         <v>11</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>0.6876541591966195</v>
+        <v>0.8384614020309604</v>
       </c>
       <c r="F5">
-        <v>0.7781042972612839</v>
+        <v>0.6432908516280571</v>
       </c>
       <c r="G5">
-        <v>0.7781042972612838</v>
+        <v>0.6432908516280571</v>
       </c>
       <c r="H5">
-        <v>0.009282074211127289</v>
+        <v>0.02487023481662192</v>
       </c>
       <c r="I5">
-        <v>-0.1007976953209697</v>
+        <v>-0.08347751687042027</v>
       </c>
       <c r="J5">
-        <v>23.49301957504819</v>
+        <v>27.77866608192901</v>
       </c>
       <c r="K5">
-        <v>24.6867053934433</v>
+        <v>28.97235190032413</v>
       </c>
     </row>
     <row r="6">
@@ -582,28 +582,28 @@
         <v>11</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>0.2635904174112546</v>
+        <v>0.1352231876127085</v>
       </c>
       <c r="F6">
-        <v>0.5589035160742397</v>
+        <v>0.1659053936123868</v>
       </c>
       <c r="G6">
-        <v>0.5589035160742399</v>
+        <v>0.1659053936123868</v>
       </c>
       <c r="H6">
-        <v>0.03931841416054248</v>
+        <v>0.2016410903691337</v>
       </c>
       <c r="I6">
-        <v>-0.067423984266064</v>
+        <v>0.112934544854593</v>
       </c>
       <c r="J6">
-        <v>32.41460344564545</v>
+        <v>21.74263053983506</v>
       </c>
       <c r="K6">
-        <v>33.60828926404056</v>
+        <v>22.93631635823017</v>
       </c>
     </row>
     <row r="7">
@@ -621,28 +621,28 @@
         <v>11</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7">
-        <v>0.1219928636081726</v>
+        <v>0.154740676256274</v>
       </c>
       <c r="F7">
-        <v>0.2413094811759975</v>
+        <v>0.2043690961520518</v>
       </c>
       <c r="G7">
-        <v>0.2413094811759975</v>
+        <v>0.2043690961520518</v>
       </c>
       <c r="H7">
-        <v>0.1488083216059181</v>
+        <v>0.1722268361960219</v>
       </c>
       <c r="I7">
-        <v>0.05423146845102</v>
+        <v>0.08025204021780219</v>
       </c>
       <c r="J7">
-        <v>34.62260230515953</v>
+        <v>20.41197796065431</v>
       </c>
       <c r="K7">
-        <v>35.81628812355465</v>
+        <v>21.60566377904942</v>
       </c>
     </row>
     <row r="8">
@@ -660,28 +660,28 @@
         <v>11</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8">
-        <v>0.3497037335674049</v>
+        <v>0.3414467889800145</v>
       </c>
       <c r="F8">
-        <v>0.9640997800475366</v>
+        <v>0.9901323226621296</v>
       </c>
       <c r="G8">
-        <v>0.9640997800475368</v>
+        <v>0.9901323226621297</v>
       </c>
       <c r="H8">
-        <v>0.0002378982173758202</v>
+        <v>1.796403892937554E-05</v>
       </c>
       <c r="I8">
-        <v>-0.1108467797584713</v>
+        <v>-0.1110911510678563</v>
       </c>
       <c r="J8">
-        <v>23.22887634248294</v>
+        <v>27.79592340336841</v>
       </c>
       <c r="K8">
-        <v>24.42256216087805</v>
+        <v>28.98960922176352</v>
       </c>
     </row>
     <row r="9">
@@ -699,28 +699,28 @@
         <v>11</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9">
-        <v>0.4337517019058801</v>
+        <v>0.04752918207841706</v>
       </c>
       <c r="F9">
-        <v>0.9344667105418158</v>
+        <v>0.07049951671919756</v>
       </c>
       <c r="G9">
-        <v>0.9344667105418158</v>
+        <v>0.07049951671919756</v>
       </c>
       <c r="H9">
-        <v>0.000793750630390865</v>
+        <v>0.3185227609170402</v>
       </c>
       <c r="I9">
-        <v>-0.1102291659662324</v>
+        <v>0.2428030676856002</v>
       </c>
       <c r="J9">
-        <v>33.18336485446272</v>
+        <v>21.73078840867091</v>
       </c>
       <c r="K9">
-        <v>34.37705067285783</v>
+        <v>22.92447422706602</v>
       </c>
     </row>
     <row r="10">
@@ -738,28 +738,28 @@
         <v>11</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10">
-        <v>0.2946144756849679</v>
+        <v>0.03613637571524328</v>
       </c>
       <c r="F10">
-        <v>0.5760922793434665</v>
+        <v>0.06212614755094788</v>
       </c>
       <c r="G10">
-        <v>0.5760922793434664</v>
+        <v>0.06212614755094788</v>
       </c>
       <c r="H10">
-        <v>0.03604075856133777</v>
+        <v>0.3349335328048116</v>
       </c>
       <c r="I10">
-        <v>-0.07106582382073579</v>
+        <v>0.2610372586720128</v>
       </c>
       <c r="J10">
-        <v>36.12952731002763</v>
+        <v>20.58769695808868</v>
       </c>
       <c r="K10">
-        <v>37.32321312842274</v>
+        <v>21.7813827764838</v>
       </c>
     </row>
     <row r="11">
@@ -777,28 +777,28 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11">
-        <v>0.6503872683131071</v>
+        <v>0.7831773928287253</v>
       </c>
       <c r="F11">
-        <v>0.8240060454694405</v>
+        <v>0.6947961370722957</v>
       </c>
       <c r="G11">
-        <v>0.8240060454694402</v>
+        <v>0.6947961370722957</v>
       </c>
       <c r="H11">
-        <v>0.006558312211902282</v>
+        <v>0.02026999469599338</v>
       </c>
       <c r="I11">
-        <v>-0.11762189876161</v>
+        <v>-0.1021962559670075</v>
       </c>
       <c r="J11">
-        <v>22.50508856659837</v>
+        <v>26.32366657378503</v>
       </c>
       <c r="K11">
-        <v>23.41284384558051</v>
+        <v>27.23142185276717</v>
       </c>
     </row>
     <row r="12">
@@ -816,28 +816,28 @@
         <v>10</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12">
-        <v>0.3010842492531833</v>
+        <v>0.1680299861036016</v>
       </c>
       <c r="F12">
-        <v>0.5872959229113653</v>
+        <v>0.1971935301958709</v>
       </c>
       <c r="G12">
-        <v>0.5872959229113652</v>
+        <v>0.1971935301958712</v>
       </c>
       <c r="H12">
-        <v>0.038425828786233</v>
+        <v>0.1982700497975259</v>
       </c>
       <c r="I12">
-        <v>-0.08177094261548778</v>
+        <v>0.09805380602221658</v>
       </c>
       <c r="J12">
-        <v>30.96304876125316</v>
+        <v>21.24751166928304</v>
       </c>
       <c r="K12">
-        <v>31.8708040402353</v>
+        <v>22.15526694826518</v>
       </c>
     </row>
     <row r="13">
@@ -855,28 +855,28 @@
         <v>10</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13">
-        <v>0.154555354914052</v>
+        <v>0.1880526673652805</v>
       </c>
       <c r="F13">
-        <v>0.2774828293025911</v>
+        <v>0.2368596318115311</v>
       </c>
       <c r="G13">
-        <v>0.2774828293025909</v>
+        <v>0.2368596318115311</v>
       </c>
       <c r="H13">
-        <v>0.145099284748026</v>
+        <v>0.1696921444590826</v>
       </c>
       <c r="I13">
-        <v>0.03823669534152918</v>
+        <v>0.06590366251646795</v>
       </c>
       <c r="J13">
-        <v>32.94015383098678</v>
+        <v>20.04764027978902</v>
       </c>
       <c r="K13">
-        <v>33.84790910996892</v>
+        <v>20.95539555877116</v>
       </c>
     </row>
   </sheetData>
